--- a/main/ig/ValueSet-fr-medication-reconciliation-document-type.xlsx
+++ b/main/ig/ValueSet-fr-medication-reconciliation-document-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:00:00+00:00</t>
+    <t>2026-05-19T09:10:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-reconciliation-document-type.xlsx
+++ b/main/ig/ValueSet-fr-medication-reconciliation-document-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T09:10:48+00:00</t>
+    <t>2026-05-27T13:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
